--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_16_R2.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_16_R2.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.7918</v>
+        <v>6.2159</v>
       </c>
       <c r="E2" t="n">
-        <v>5.9691</v>
+        <v>4.6283</v>
       </c>
       <c r="F2" t="n">
-        <v>1.8228</v>
+        <v>1.5875</v>
       </c>
       <c r="G2" t="n">
         <v>5.0598</v>
@@ -610,13 +610,13 @@
         <v>1.6237</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3041</v>
+        <v>0.7281</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9189</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3853</v>
+        <v>0.15</v>
       </c>
       <c r="V2" t="n">
         <v>1.3558</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.3821</v>
+        <v>6.1791</v>
       </c>
       <c r="E3" t="n">
-        <v>5.445</v>
+        <v>4.9732</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9371</v>
+        <v>1.2059</v>
       </c>
       <c r="G3" t="n">
         <v>4.1794</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1125</v>
+        <v>-0.0905</v>
       </c>
       <c r="T3" t="n">
-        <v>0.2715</v>
+        <v>-0.2003</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.159</v>
+        <v>0.1098</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.3495</v>
+        <v>4.7451</v>
       </c>
       <c r="E4" t="n">
-        <v>2.4271</v>
+        <v>3.0916</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9224</v>
+        <v>1.6535</v>
       </c>
       <c r="G4" t="n">
         <v>6.1924</v>
@@ -766,13 +766,13 @@
         <v>2.5515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.2346</v>
+        <v>0.161</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7389</v>
+        <v>-0.0745</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5043</v>
+        <v>0.2355</v>
       </c>
       <c r="V4" t="n">
         <v>-1.6083</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. BLOSSOMGAME</t>
+          <t>A. DIALLO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.3586</v>
+        <v>2.9962</v>
       </c>
       <c r="E5" t="n">
-        <v>2.6753</v>
+        <v>0.8494</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6834</v>
+        <v>2.1469</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1858</v>
+        <v>1.6626</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0419</v>
+        <v>-1.6399</v>
       </c>
       <c r="I5" t="n">
-        <v>0.144</v>
+        <v>3.3025</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5658</v>
+        <v>1.1558</v>
       </c>
       <c r="K5" t="n">
-        <v>1.4186</v>
+        <v>-0.5238</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1472</v>
+        <v>1.6796</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.38</v>
+        <v>0.5068</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.3767</v>
+        <v>-1.1161</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0033</v>
+        <v>1.6229</v>
       </c>
       <c r="P5" t="n">
-        <v>1.8556</v>
+        <v>2.3195</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>2.5515</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0337</v>
+        <v>0.0863</v>
       </c>
       <c r="T5" t="n">
-        <v>0.8259</v>
+        <v>-0.0745</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2078</v>
+        <v>0.1608</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2836</v>
+        <v>-1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIALLO</t>
+          <t>M. STRAZEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>2.4662</v>
+        <v>2.8859</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1849</v>
+        <v>0.6398</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2813</v>
+        <v>2.2461</v>
       </c>
       <c r="G6" t="n">
-        <v>1.6626</v>
+        <v>2.2245</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6399</v>
+        <v>-1.7874</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3025</v>
+        <v>4.0119</v>
       </c>
       <c r="J6" t="n">
-        <v>1.1558</v>
+        <v>1.9999</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.5238</v>
+        <v>-1.0181</v>
       </c>
       <c r="L6" t="n">
-        <v>1.6796</v>
+        <v>3.018</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5068</v>
+        <v>0.2246</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1161</v>
+        <v>-0.7692</v>
       </c>
       <c r="O6" t="n">
-        <v>1.6229</v>
+        <v>0.9939</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3195</v>
+        <v>0.6959</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-1.3917</v>
       </c>
       <c r="R6" t="n">
-        <v>2.5515</v>
+        <v>2.0876</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4437</v>
+        <v>-0.0345</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7389</v>
+        <v>0.0316</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2952</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>M. STRAZEL</t>
+          <t>J. BLOSSOMGAME</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.9025</v>
+        <v>2.6681</v>
       </c>
       <c r="E7" t="n">
-        <v>0.09329999999999999</v>
+        <v>2.0855</v>
       </c>
       <c r="F7" t="n">
-        <v>1.8092</v>
+        <v>0.5826</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2245</v>
+        <v>0.1858</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7874</v>
+        <v>0.0419</v>
       </c>
       <c r="I7" t="n">
-        <v>4.0119</v>
+        <v>0.144</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9999</v>
+        <v>1.5658</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0181</v>
+        <v>1.4186</v>
       </c>
       <c r="L7" t="n">
-        <v>3.018</v>
+        <v>0.1472</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2246</v>
+        <v>-1.38</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7692</v>
+        <v>-1.3767</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9939</v>
+        <v>-0.0033</v>
       </c>
       <c r="P7" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.3917</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0179</v>
+        <v>0.3431</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5149</v>
+        <v>0.2361</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.503</v>
+        <v>0.107</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7046</v>
+        <v>1.3952</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8793</v>
+        <v>1.469</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1747</v>
+        <v>-0.0738</v>
       </c>
       <c r="G8" t="n">
         <v>0.6245000000000001</v>
@@ -1078,13 +1078,13 @@
         <v>2.0876</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.9353</v>
+        <v>-0.2447</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.2317</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1138</v>
+        <v>-0.013</v>
       </c>
       <c r="V8" t="n">
         <v>-1.0722</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4632</v>
+        <v>-0.6826</v>
       </c>
       <c r="E9" t="n">
-        <v>0.843</v>
+        <v>0.4892</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3062</v>
+        <v>-1.1718</v>
       </c>
       <c r="G9" t="n">
         <v>-0.5894</v>
@@ -1156,13 +1156,13 @@
         <v>1.1598</v>
       </c>
       <c r="S9" t="n">
-        <v>0.0387</v>
+        <v>-0.1808</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2636</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2249</v>
+        <v>-0.0905</v>
       </c>
       <c r="V9" t="n">
         <v>-1.0722</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0135</v>
+        <v>-1.4334</v>
       </c>
       <c r="E10" t="n">
-        <v>0.601</v>
+        <v>1.1475</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6145</v>
+        <v>-2.5809</v>
       </c>
       <c r="G10" t="n">
         <v>0.9641999999999999</v>
@@ -1234,13 +1234,13 @@
         <v>2.3195</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.0627</v>
+        <v>-0.4826</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.7468</v>
+        <v>-0.2003</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3159</v>
+        <v>-0.2822</v>
       </c>
       <c r="V10" t="n">
         <v>-3.0748</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.9867</v>
+        <v>-3.104</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8236</v>
+        <v>-1.7056</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.1631</v>
+        <v>-1.3984</v>
       </c>
       <c r="G11" t="n">
         <v>-1.4352</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2473</v>
+        <v>-0.3646</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.5228</v>
+        <v>-0.4048</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2754</v>
+        <v>0.0402</v>
       </c>
       <c r="V11" t="n">
         <v>-1.0722</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>21.4919</v>
+        <v>21.8655</v>
       </c>
       <c r="E12" t="n">
-        <v>17.2944</v>
+        <v>17.6679</v>
       </c>
       <c r="F12" t="n">
-        <v>4.197699999999999</v>
+        <v>4.1976</v>
       </c>
       <c r="G12" t="n">
         <v>19.0686</v>
@@ -1390,13 +1390,13 @@
         <v>18.5563</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4525</v>
+        <v>-0.07919999999999994</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8039000000000001</v>
+        <v>-0.4306000000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3513999999999999</v>
+        <v>0.3514999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>-6.402100000000001</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>F. PETRUSEV</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.9016</v>
+        <v>2.0456</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3504</v>
+        <v>2.885</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.4489</v>
+        <v>-0.8394</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3014</v>
+        <v>-2.1076</v>
       </c>
       <c r="H13" t="n">
-        <v>2.7741</v>
+        <v>-1.2712</v>
       </c>
       <c r="I13" t="n">
-        <v>-2.4727</v>
+        <v>-0.8365</v>
       </c>
       <c r="J13" t="n">
-        <v>2.7536</v>
+        <v>0.284</v>
       </c>
       <c r="K13" t="n">
-        <v>3.7006</v>
+        <v>-0.1443</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.947</v>
+        <v>0.4282</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.4522</v>
+        <v>-2.3916</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.9265</v>
+        <v>-1.1269</v>
       </c>
       <c r="O13" t="n">
-        <v>-1.5257</v>
+        <v>-1.2647</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.232</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R13" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>1.9017</v>
+        <v>0.9366</v>
       </c>
       <c r="T13" t="n">
-        <v>1.6122</v>
+        <v>0.0081</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2895</v>
+        <v>0.9285</v>
       </c>
       <c r="V13" t="n">
-        <v>0.9304</v>
+        <v>3.2166</v>
       </c>
       <c r="W13" t="n">
-        <v>2.1444</v>
+        <v>3.7527</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.214</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>F. PETRUSEV</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.5433</v>
+        <v>1.8128</v>
       </c>
       <c r="E14" t="n">
-        <v>2.7671</v>
+        <v>4.4068</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2238</v>
+        <v>-2.5941</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.1076</v>
+        <v>0.3014</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.2712</v>
+        <v>2.7741</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8365</v>
+        <v>-2.4727</v>
       </c>
       <c r="J14" t="n">
-        <v>0.284</v>
+        <v>2.7536</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.1443</v>
+        <v>3.7006</v>
       </c>
       <c r="L14" t="n">
-        <v>0.4282</v>
+        <v>-0.947</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.3916</v>
+        <v>-2.4522</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1269</v>
+        <v>-0.9265</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.2647</v>
+        <v>-1.5257</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>-0.232</v>
       </c>
       <c r="Q14" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R14" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4343</v>
+        <v>0.8129</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1098</v>
+        <v>0.6686</v>
       </c>
       <c r="U14" t="n">
-        <v>1.5442</v>
+        <v>0.1443</v>
       </c>
       <c r="V14" t="n">
-        <v>3.2166</v>
+        <v>0.9304</v>
       </c>
       <c r="W14" t="n">
-        <v>3.7527</v>
+        <v>2.1444</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5361</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2955</v>
+        <v>0.5479000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.2839</v>
+        <v>-0.166</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5794</v>
+        <v>0.7138</v>
       </c>
       <c r="G15" t="n">
         <v>1.2779</v>
@@ -1624,13 +1624,13 @@
         <v>0.232</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.449</v>
+        <v>-0.1966</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2987</v>
+        <v>-0.1808</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1502</v>
+        <v>-0.0158</v>
       </c>
       <c r="V15" t="n">
         <v>0.3943</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.4973</v>
+        <v>-0.43</v>
       </c>
       <c r="E16" t="n">
         <v>-0.1736</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3236</v>
+        <v>-0.2564</v>
       </c>
       <c r="G16" t="n">
         <v>0.1538</v>
@@ -1702,13 +1702,13 @@
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.651</v>
+        <v>-0.5838</v>
       </c>
       <c r="T16" t="n">
         <v>-0.224</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.3506</v>
+        <v>-1.0982</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.2738</v>
+        <v>-0.1559</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.0767</v>
+        <v>-0.9423</v>
       </c>
       <c r="G17" t="n">
         <v>-0.9842</v>
@@ -1780,13 +1780,13 @@
         <v>0.4639</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8303</v>
+        <v>-0.5779</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4481</v>
+        <v>-0.3301</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3822</v>
+        <v>-0.2478</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.8179</v>
+        <v>-1.4139</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0357</v>
+        <v>-0.7998</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7821</v>
+        <v>-0.6141</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6312</v>
@@ -1858,13 +1858,13 @@
         <v>0.232</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4187</v>
+        <v>-0.0147</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3734</v>
+        <v>-0.1375</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0452</v>
+        <v>0.1228</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>M. WRIGHT IV</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.3113</v>
+        <v>-2.552</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1085</v>
+        <v>0.0965</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2029</v>
+        <v>-2.6484</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.8006</v>
+        <v>-0.8172</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0311</v>
+        <v>1.9532</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7695</v>
+        <v>-2.7704</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9475</v>
+        <v>3.1934</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8739</v>
+        <v>3.2805</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0736</v>
+        <v>-0.0871</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.7481</v>
+        <v>-4.0106</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.9049</v>
+        <v>-1.3273</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.8431</v>
+        <v>-2.6834</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.8556</v>
+        <v>-3.0154</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-4.639</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3448</v>
+        <v>0.2084</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2636</v>
+        <v>-0.208</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0813</v>
+        <v>0.4165</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9219</v>
+        <v>-2.7495</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.0038</v>
+        <v>-1.5803</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9181</v>
+        <v>-1.1693</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.735</v>
+        <v>-0.8006</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4525</v>
+        <v>-0.0311</v>
       </c>
       <c r="I20" t="n">
-        <v>-3.2826</v>
+        <v>-0.7695</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.8297</v>
+        <v>0.9475</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1379</v>
+        <v>0.8739</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9676</v>
+        <v>0.0736</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9053</v>
+        <v>-1.7481</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.5904</v>
+        <v>-0.9049</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.3149</v>
+        <v>-0.8431</v>
       </c>
       <c r="P20" t="n">
-        <v>0.9278</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-2.3195</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5632</v>
+        <v>-0.0934</v>
       </c>
       <c r="T20" t="n">
-        <v>0.8259</v>
+        <v>-0.2082</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2627</v>
+        <v>0.1149</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6778999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>M. WRIGHT IV</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.9052</v>
+        <v>-3.428</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.9651</v>
+        <v>-1.7115</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.9401</v>
+        <v>-1.7165</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.8172</v>
+        <v>-3.735</v>
       </c>
       <c r="H21" t="n">
-        <v>1.9532</v>
+        <v>-0.4525</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.7704</v>
+        <v>-3.2826</v>
       </c>
       <c r="J21" t="n">
-        <v>3.1934</v>
+        <v>-1.8297</v>
       </c>
       <c r="K21" t="n">
-        <v>3.2805</v>
+        <v>0.1379</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.0871</v>
+        <v>-1.9676</v>
       </c>
       <c r="M21" t="n">
-        <v>-4.0106</v>
+        <v>-1.9053</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.3273</v>
+        <v>-0.5904</v>
       </c>
       <c r="O21" t="n">
-        <v>-2.6834</v>
+        <v>-1.3149</v>
       </c>
       <c r="P21" t="n">
-        <v>-3.0154</v>
+        <v>0.9278</v>
       </c>
       <c r="Q21" t="n">
-        <v>-4.639</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.6237</v>
+        <v>0.9278</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.1448</v>
+        <v>0.0571</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.2696</v>
+        <v>0.1182</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1248</v>
+        <v>-0.0611</v>
       </c>
       <c r="V21" t="n">
-        <v>1.0722</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="W21" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>-0.6778999999999999</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.0269</v>
+        <v>-4.0219</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.8232</v>
+        <v>-2.1771</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2037</v>
+        <v>-1.8448</v>
       </c>
       <c r="G22" t="n">
         <v>-4.7938</v>
@@ -2170,13 +2170,13 @@
         <v>1.1598</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4059</v>
+        <v>0.411</v>
       </c>
       <c r="T22" t="n">
-        <v>0.5272</v>
+        <v>0.1733</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1212</v>
+        <v>0.2377</v>
       </c>
       <c r="V22" t="n">
         <v>2.6805</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. ANDERSON</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.6582</v>
+        <v>-4.625</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2918</v>
+        <v>-1.294</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3664</v>
+        <v>-3.331</v>
       </c>
       <c r="G23" t="n">
-        <v>-3.1017</v>
+        <v>-2.8303</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.6529</v>
+        <v>-0.4981</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.4488</v>
+        <v>-2.3322</v>
       </c>
       <c r="J23" t="n">
-        <v>-2.3828</v>
+        <v>1.1588</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.8837</v>
+        <v>0.9649</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.4991</v>
+        <v>0.1939</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.719</v>
+        <v>-3.9891</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7692</v>
+        <v>-1.463</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0502</v>
+        <v>-2.5261</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q23" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>0.0672</v>
+        <v>0.347</v>
       </c>
       <c r="T23" t="n">
-        <v>0.3383</v>
+        <v>-0.1333</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.271</v>
+        <v>0.4804</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.214</v>
       </c>
       <c r="W23" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.0722</v>
+        <v>-1.214</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>J. ANDERSON</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.743</v>
+        <v>-4.7933</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3556</v>
+        <v>-3.5277</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.3874</v>
+        <v>-1.2656</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.8303</v>
+        <v>-3.1017</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.4981</v>
+        <v>-1.6529</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3322</v>
+        <v>-1.4488</v>
       </c>
       <c r="J24" t="n">
-        <v>1.1588</v>
+        <v>-2.3828</v>
       </c>
       <c r="K24" t="n">
-        <v>0.9649</v>
+        <v>-0.8837</v>
       </c>
       <c r="L24" t="n">
-        <v>0.1939</v>
+        <v>-1.4991</v>
       </c>
       <c r="M24" t="n">
-        <v>-3.9891</v>
+        <v>-0.719</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.463</v>
+        <v>-0.7692</v>
       </c>
       <c r="O24" t="n">
-        <v>-2.5261</v>
+        <v>0.0502</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9278</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q24" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3917</v>
+        <v>0.6959</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.771</v>
+        <v>-0.0679</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.1949</v>
+        <v>0.1024</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4239</v>
+        <v>-0.1702</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.214</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.214</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-21.4919</v>
+        <v>-20.7055</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.1975</v>
+        <v>-4.1976</v>
       </c>
       <c r="F25" t="n">
-        <v>-17.2943</v>
+        <v>-16.5081</v>
       </c>
       <c r="G25" t="n">
         <v>-19.0685</v>
@@ -2377,10 +2377,10 @@
         <v>-17.8511</v>
       </c>
       <c r="J25" t="n">
-        <v>3.310099999999998</v>
+        <v>3.310100000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>9.049300000000001</v>
+        <v>9.049300000000002</v>
       </c>
       <c r="L25" t="n">
         <v>-5.7394</v>
@@ -2404,16 +2404,16 @@
         <v>9.2783</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4522999999999994</v>
+        <v>1.2387</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3513000000000002</v>
+        <v>-0.3513000000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>0.8042</v>
+        <v>1.5904</v>
       </c>
       <c r="V25" t="n">
-        <v>6.402100000000001</v>
+        <v>6.402099999999999</v>
       </c>
       <c r="W25" t="n">
         <v>11.3999</v>
